--- a/app/pipeline_output/werize/mapping_werize_COMBINED.xlsx
+++ b/app/pipeline_output/werize/mapping_werize_COMBINED.xlsx
@@ -47,7 +47,7 @@
       <color rgb="00FF0000"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
         <bgColor rgb="00FED8B1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-        <bgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,9 +121,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -767,17 +758,17 @@
           <t>customer.customerBankAccounts.0.accountNumber</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>0.85</v>
+      <c r="F6" s="4" t="n">
+        <v>0.92</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'accountNo' → 'CUSTOMERBANKACCOUNTNUMBER' (frequency=9)</t>
+          <t>Alias match (tier2): 'accountNo' → 'CUSTOMERBANKACCOUNTNUMBER' (frequency=10)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -822,7 +813,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a fundamental demographic attribute of the applicant.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a standard demographic detail of the applicant.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -912,7 +903,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'apr' → 'ANNUALIZEDPERCENTAGE' (frequency=58)</t>
+          <t>Alias match (tier1): 'apr' → 'ANNUALIZEDPERCENTAGE' (frequency=59)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1002,7 +993,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'bankBranchName' → 'CUSTOMERBANKBRANCH' (frequency=12)</t>
+          <t>Alias match (tier2): 'bankBranchName' → 'CUSTOMERBANKBRANCH' (frequency=13)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1047,7 +1038,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'bankName' → 'CUSTOMERBANK' (frequency=23)</t>
+          <t>Alias match (tier2): 'bankName' → 'CUSTOMERBANK' (frequency=24)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1069,7 +1060,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1114,17 +1105,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME2</t>
+          <t>DOCUMENTNAME1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.1.document</t>
+          <t>loanAccount.loanDocuments.0.document</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
@@ -1182,7 +1173,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credential for accessing an applicant's personal bank statement document.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This relates to the applicant's personal bank account credentials for verification.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1204,17 +1195,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID3</t>
+          <t>DOCUMENTID2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.2.documentId</t>
+          <t>loanAccount.loanDocuments.1.documentId</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
@@ -1249,17 +1240,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME4</t>
+          <t>DOCUMENTNAME2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.3.document</t>
+          <t>loanAccount.loanDocuments.1.document</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
@@ -1317,7 +1308,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credential for accessing an applicant's personal bank statement document.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This relates to the applicant's personal bank account credentials for verification.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1339,17 +1330,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID5</t>
+          <t>DOCUMENTID3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.4.documentId</t>
+          <t>loanAccount.loanDocuments.2.documentId</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
@@ -1384,17 +1375,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME6</t>
+          <t>DOCUMENTNAME3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.5.document</t>
+          <t>loanAccount.loanDocuments.2.document</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
@@ -1452,7 +1443,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credential for accessing an applicant's personal bank statement document.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This relates to the applicant's personal bank account credentials for verification.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1474,17 +1465,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID7</t>
+          <t>DOCUMENTID4</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.6.documentId</t>
+          <t>loanAccount.loanDocuments.3.documentId</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
@@ -1519,17 +1510,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME8</t>
+          <t>DOCUMENTNAME4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.7.document</t>
+          <t>loanAccount.loanDocuments.3.document</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
@@ -1587,7 +1578,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credential for accessing an applicant's personal bank statement document.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This relates to the applicant's personal bank account credentials for verification.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1609,17 +1600,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID9</t>
+          <t>DOCUMENTID5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.8.documentId</t>
+          <t>loanAccount.loanDocuments.4.documentId</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
@@ -1654,17 +1645,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME10</t>
+          <t>DOCUMENTNAME5</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.9.document</t>
+          <t>loanAccount.loanDocuments.4.document</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
@@ -1722,7 +1713,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credential for accessing an applicant's personal bank statement document.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This relates to the applicant's personal bank account credentials for verification.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1744,17 +1735,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID11</t>
+          <t>DOCUMENTID6</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.10.documentId</t>
+          <t>loanAccount.loanDocuments.5.documentId</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
@@ -1789,17 +1780,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME12</t>
+          <t>DOCUMENTNAME6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.11.document</t>
+          <t>loanAccount.loanDocuments.5.document</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
@@ -1857,7 +1848,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credential for accessing an applicant's personal bank statement document.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This relates to the applicant's personal bank account credentials for verification.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1879,17 +1870,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID13</t>
+          <t>DOCUMENTID7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.12.documentId</t>
+          <t>loanAccount.loanDocuments.6.documentId</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
@@ -1924,17 +1915,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME14</t>
+          <t>DOCUMENTNAME7</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.13.document</t>
+          <t>loanAccount.loanDocuments.6.document</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
@@ -1992,7 +1983,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credential for accessing an applicant's personal bank statement document.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This relates to the applicant's personal bank account credentials for verification.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2014,17 +2005,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME15</t>
+          <t>DOCUMENTNAME8</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.14.document</t>
+          <t>loanAccount.loanDocuments.7.document</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
@@ -2064,12 +2055,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID16</t>
+          <t>DOCUMENTID8</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.15.documentId</t>
+          <t>loanAccount.loanDocuments.7.documentId</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
@@ -2109,12 +2100,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID17</t>
+          <t>DOCUMENTID9</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.16.documentId</t>
+          <t>loanAccount.loanDocuments.8.documentId</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
@@ -2149,17 +2140,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID18</t>
+          <t>DOCUMENTID10</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.17.documentId</t>
+          <t>loanAccount.loanDocuments.9.documentId</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
@@ -2194,17 +2185,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME19</t>
+          <t>DOCUMENTNAME9</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.18.document</t>
+          <t>loanAccount.loanDocuments.8.document</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
@@ -2329,17 +2320,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME20</t>
+          <t>DOCUMENTNAME10</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.19.document</t>
+          <t>loanAccount.loanDocuments.9.document</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
@@ -2374,7 +2365,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2397,7 +2388,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a unique identifier for a credit bureau enquiry, which is part of the loan application and underwriting process.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a unique identifier for the credit bureau check performed for this specific loan application.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2442,7 +2433,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'clientLoanId' → 'LOANID' (frequency=6)</t>
+          <t>Alias match (tier3): 'clientLoanId' → 'LOANID' (frequency=7)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2487,7 +2478,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'currentAddress' → 'APPLICANTCOMMADDRESSDOORNO' (frequency=6)</t>
+          <t>Alias match (tier3): 'currentAddress' → 'APPLICANTCOMMADDRESSDOORNO' (frequency=7)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2532,7 +2523,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's current residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a component of the applicant's current residential address.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2622,7 +2613,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's current residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a component of the applicant's current residential address.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2667,7 +2658,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's current residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a component of the applicant's current residential address.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2869,7 +2860,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2892,7 +2883,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a system-generated status message related to the application's deduplication check process.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a status message from an underwriting process (deduplication check) for the loan application.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2914,7 +2905,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2937,7 +2928,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a status message from a deduplication check, which is an application-level underwriting step.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a status message from an underwriting process (deduplication check) for the loan application.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3072,7 +3063,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is the applicant's employment address, a core part of their personal profile.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is the applicant's office address, part of their employment profile.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3117,7 +3108,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is the name of the applicant's employer, which is part of their employment profile.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is the name of the applicant's employer, part of their employment profile.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3162,7 +3153,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'employmentType' → 'EMPLOYMENTSTATUS' (frequency=46)</t>
+          <t>Alias match (tier1): 'employmentType' → 'EMPLOYMENTSTATUS' (frequency=47)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3207,7 +3198,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'fatherName' → 'APPLICANTFATHERNAME' (frequency=43)</t>
+          <t>Alias match (tier1): 'fatherName' → 'APPLICANTFATHERNAME' (frequency=44)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3252,7 +3243,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'firstName' → 'APPLICANTCUSTOMERNAME' (frequency=42)</t>
+          <t>Alias match (tier1): 'firstName' → 'APPLICANTCUSTOMERNAME' (frequency=45)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3319,7 +3310,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3342,7 +3333,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. FOIR (Fixed Obligation to Income Ratio) is a key calculated underwriting metric used to determine loan eligibility.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. FOIR is a key derived underwriting metric used to assess loan eligibility at the application level.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3499,7 +3490,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3522,7 +3513,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a loan-specific date that defines the start of interest accrual, a core loan term.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific term of the loan related to the repayment structure.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3634,17 +3625,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID21</t>
+          <t>DOCUMENTID11</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.20.documentId</t>
+          <t>loanAccount.loanDocuments.10.documentId</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
@@ -3679,17 +3670,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME22</t>
+          <t>DOCUMENTNAME11</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.21.document</t>
+          <t>loanAccount.loanDocuments.10.document</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
@@ -3747,7 +3738,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'lastName' → 'APPLICANTLASTNAME' (frequency=38)</t>
+          <t>Alias match (tier1): 'lastName' → 'APPLICANTLASTNAME' (frequency=41)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3774,12 +3765,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME23</t>
+          <t>DOCUMENTNAME12</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.22.document</t>
+          <t>loanAccount.loanDocuments.11.document</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
@@ -3882,7 +3873,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'loanEmi' → 'APPLICANTPROPOSEDEMI' (frequency=17)</t>
+          <t>Alias match (tier2): 'loanEmi' → 'APPLICANTPROPOSEDEMI' (frequency=18)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3892,54 +3883,54 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>maritalStatus</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>MARITALSTATUS</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>customer.maritalStatus</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Exact match: normalized 'maritalStatus' matches 'MARITALSTATUS'</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>loanType</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERTYPE</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.customerType</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>alias_tier4</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Alias match (tier4): 'loanType' → 'APPLICANTCUSTOMERTYPE' (frequency=1)</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>MasDedupeReferceId</t>
+          <t>maritalStatus</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3949,17 +3940,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER6</t>
+          <t>MARITALSTATUS</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.6.value</t>
+          <t>customer.maritalStatus</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
@@ -3967,12 +3958,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a system-generated reference ID from an application-level deduplication check.</t>
+          <t>Exact match: normalized 'maritalStatus' matches 'MARITALSTATUS'</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3984,7 +3975,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>mobileNumber</t>
+          <t>MasDedupeReferceId</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3999,12 +3990,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>MOBILENUMBER</t>
+          <t>LOANPARAMETER6</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>customer.mobilePhone</t>
+          <t>loanAccount.loanParameters.6.value</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
@@ -4012,12 +4003,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'mobileNumber' matches 'MOBILENUMBER'</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a reference ID for a deduplication check, which is an underwriting process for the loan application.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4029,7 +4020,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>motherName</t>
+          <t>mobileNumber</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4044,25 +4035,25 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTMOTHERNAME</t>
+          <t>MOBILENUMBER</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.motherName</t>
+          <t>customer.mobilePhone</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'motherName' → 'APPLICANTMOTHERNAME' (frequency=39)</t>
+          <t>Exact match: normalized 'mobileNumber' matches 'MOBILENUMBER'</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4074,7 +4065,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>nationality</t>
+          <t>motherName</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4089,25 +4080,25 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOUNTRY</t>
+          <t>APPLICANTMOTHERNAME</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.country</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.motherName</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0.98</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'nationality' → 'APPLICANTCOUNTRY' (frequency=8)</t>
+          <t>Alias match (tier1): 'motherName' → 'APPLICANTMOTHERNAME' (frequency=40)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4119,7 +4110,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>netMonthlyIncome</t>
+          <t>nationality</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4134,25 +4125,25 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>BORROWERINCOME</t>
+          <t>APPLICANTCOUNTRY</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.netIncomeOfBorrower</t>
+          <t>loanAccount.customer.country</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'netMonthlyIncome' → 'BORROWERINCOME' (frequency=31)</t>
+          <t>Alias match (tier2): 'nationality' → 'APPLICANTCOUNTRY' (frequency=10)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4164,7 +4155,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>numberOfRepayments</t>
+          <t>netMonthlyIncome</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4174,30 +4165,30 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER7</t>
+          <t>BORROWERINCOME</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.7.value</t>
+          <t>loanAccount.loanAccountAdditional.netIncomeOfBorrower</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This defines the loan's tenure, which is a fundamental component of the loan structure.</t>
+          <t>Alias match (tier1): 'netMonthlyIncome' → 'BORROWERINCOME' (frequency=32)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4209,7 +4200,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>numberOfRepayments</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4224,25 +4215,25 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTOCCUPATION</t>
+          <t>LOANPARAMETER7</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.occupation1</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.7.value</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'occupation' → 'APPLICANTOCCUPATION' (frequency=8)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This field represents the loan tenure, a core parameter of the loan's repayment structure.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4254,7 +4245,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>otherCharges</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4264,30 +4255,30 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>FEE2</t>
+          <t>APPLICANTOCCUPATION</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee2</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>0.9</v>
+          <t>loanAccount.customer.occupation1</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (charges, charge)</t>
+          <t>Alias match (tier3): 'occupation' → 'APPLICANTOCCUPATION' (frequency=8)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4299,7 +4290,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>panLink</t>
+          <t>otherCharges</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4309,30 +4300,30 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTIDENTITYPROOFIMAGEID</t>
+          <t>FEE2</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.identityProofImageId</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.fee2</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0.9</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'panLink' → 'APPLICANTIDENTITYPROOFIMAGEID' (frequency=5)</t>
+          <t>Fee detection: field contains fee/charge keywords (charge, charges)</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4344,7 +4335,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>panNumber</t>
+          <t>panLink</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4359,25 +4350,25 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>PANNUMBER</t>
+          <t>APPLICANTIDENTITYPROOFIMAGEID</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>customer.panNo</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.identityProofImageId</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'panNumber' matches 'PANNUMBER'</t>
+          <t>Alias match (tier3): 'panLink' → 'APPLICANTIDENTITYPROOFIMAGEID' (frequency=5)</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4389,7 +4380,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>partnerCode</t>
+          <t>panNumber</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4404,12 +4395,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>PARTNERCODE</t>
+          <t>PANNUMBER</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.partnerCode</t>
+          <t>customer.panNo</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
@@ -4422,7 +4413,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'partnerCode' matches 'PARTNERCODE'</t>
+          <t>Exact match: normalized 'panNumber' matches 'PANNUMBER'</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4434,7 +4425,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>perfiosExcelLink</t>
+          <t>partnerCode</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4444,30 +4435,30 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID24</t>
+          <t>PARTNERCODE</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.23.documentId</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.partnerCode</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'perfiosExcelLink' → 'DOCUMENTID12' (frequency=5)</t>
+          <t>Exact match: normalized 'partnerCode' matches 'PARTNERCODE'</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4479,7 +4470,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>perfiosExcelName</t>
+          <t>perfiosExcelLink</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4489,17 +4480,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME25</t>
+          <t>DOCUMENTID12</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.24.document</t>
+          <t>loanAccount.loanDocuments.11.documentId</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -4512,7 +4503,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'perfiosExcelName' → 'DOCUMENTNAME12' (frequency=5)</t>
+          <t>Alias match (tier3): 'perfiosExcelLink' → 'DOCUMENTID12' (frequency=5)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4524,7 +4515,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>perfiosLink</t>
+          <t>perfiosExcelName</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4534,17 +4525,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID26</t>
+          <t>DOCUMENTNAME13</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.25.documentId</t>
+          <t>loanAccount.loanDocuments.12.document</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -4557,7 +4548,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'perfiosLink' → 'DOCUMENTID2' (frequency=4)</t>
+          <t>Alias match (tier3): 'perfiosExcelName' → 'DOCUMENTNAME12' (frequency=5)</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4569,7 +4560,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>perfiosName</t>
+          <t>perfiosLink</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4579,17 +4570,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME27</t>
+          <t>DOCUMENTID13</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.26.document</t>
+          <t>loanAccount.loanDocuments.12.documentId</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
@@ -4602,7 +4593,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'perfiosName' → 'DOCUMENTNAME2' (frequency=5)</t>
+          <t>Alias match (tier3): 'perfiosLink' → 'DOCUMENTID2' (frequency=4)</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4614,7 +4605,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>permanentAddress</t>
+          <t>perfiosName</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4629,12 +4620,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTBUSINESSADDRESS1</t>
+          <t>DOCUMENTNAME14</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.doorNo</t>
+          <t>loanAccount.loanDocuments.13.document</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
@@ -4647,7 +4638,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'permanentAddress' → 'APPLICANTBUSINESSADDRESS1' (frequency=6)</t>
+          <t>Alias match (tier3): 'perfiosName' → 'DOCUMENTNAME2' (frequency=5)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4659,7 +4650,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>permanentCity</t>
+          <t>permanentAddress</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4674,25 +4665,25 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM14</t>
+          <t>APPLICANTBUSINESSADDRESS1</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.doorNo</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's permanent residential address.</t>
+          <t>Alias match (tier3): 'permanentAddress' → 'APPLICANTBUSINESSADDRESS1' (frequency=7)</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4704,7 +4695,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>permanentDistrict</t>
+          <t>permanentCity</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4719,12 +4710,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM15</t>
+          <t>LOANAPPLICANTPARAM14</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
@@ -4737,7 +4728,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's permanent residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a component of the applicant's permanent residential address.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4749,7 +4740,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>permanentPincode</t>
+          <t>permanentDistrict</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4764,25 +4755,25 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERPINCODE</t>
+          <t>LOANAPPLICANTPARAM15</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.pincode</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'permanentPincode' → 'APPLICANTCUSTOMERPINCODE' (frequency=7)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a component of the applicant's permanent residential address.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4794,7 +4785,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>permanentState</t>
+          <t>permanentPincode</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4809,25 +4800,25 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM16</t>
+          <t>APPLICANTCUSTOMERPINCODE</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.pincode</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's permanent residential address.</t>
+          <t>Alias match (tier3): 'permanentPincode' → 'APPLICANTCUSTOMERPINCODE' (frequency=9)</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -4839,7 +4830,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>photoLink</t>
+          <t>permanentState</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4854,25 +4845,25 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>CUSTOMERPHOTO</t>
+          <t>LOANAPPLICANTPARAM16</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.photoImageId</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'photoLink' → 'CUSTOMERPHOTO' (frequency=6)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a component of the applicant's permanent residential address.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4884,7 +4875,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>preEmi</t>
+          <t>photoLink</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4894,17 +4885,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>FEE3</t>
+          <t>CUSTOMERPHOTO</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee3</t>
+          <t>loanAccount.customer.photoImageId</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
@@ -4917,7 +4908,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'preEmi' → 'FEE5' (frequency=5)</t>
+          <t>Alias match (tier3): 'photoLink' → 'CUSTOMERPHOTO' (frequency=7)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4929,7 +4920,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>principalAmount</t>
+          <t>preEmi</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4944,12 +4935,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>LOANAMT</t>
+          <t>FEE3</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAmount</t>
+          <t>loanAccount.fee3</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -4962,7 +4953,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'principalAmount' → 'LOANAMT' (frequency=6)</t>
+          <t>Alias match (tier3): 'preEmi' → 'FEE5' (frequency=5)</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -4974,7 +4965,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>processingFeePercentage</t>
+          <t>principalAmount</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4984,17 +4975,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTFEEPERCENTAGE</t>
+          <t>LOANAMT</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.processingFeePercentage</t>
+          <t>loanAccount.loanAmount</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
@@ -5007,7 +4998,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'processingFeePercentage' → 'APPLICANTFEEPERCENTAGE' (frequency=7)</t>
+          <t>Alias match (tier3): 'principalAmount' → 'LOANAMT' (frequency=7)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5019,7 +5010,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>productId</t>
+          <t>processingFeePercentage</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5029,17 +5020,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>PRODUCTCODE</t>
+          <t>APPLICANTFEEPERCENTAGE</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.productCode</t>
+          <t>loanAccount.processingFeePercentage</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -5052,7 +5043,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'productId' → 'PRODUCTCODE' (frequency=5)</t>
+          <t>Alias match (tier3): 'processingFeePercentage' → 'APPLICANTFEEPERCENTAGE' (frequency=8)</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5064,7 +5055,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>productType</t>
+          <t>productId</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5079,25 +5070,25 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>PRODUCTTYPE</t>
+          <t>PRODUCTCODE</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.productType</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.productCode</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'productType' matches 'PRODUCTTYPE'</t>
+          <t>Alias match (tier3): 'productId' → 'PRODUCTCODE' (frequency=5)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5109,7 +5100,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>profileId</t>
+          <t>productType</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5119,30 +5110,30 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>APPLICATIONFILEID</t>
+          <t>PRODUCTTYPE</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.applicationFileId</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.productType</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'profileId' → 'APPLICATIONFILEID' (frequency=6)</t>
+          <t>Exact match: normalized 'productType' matches 'PRODUCTTYPE'</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5154,7 +5145,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>profileId</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5164,30 +5155,30 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>LOANPURPOSE1</t>
+          <t>APPLICATIONFILEID</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanPurpose1</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="n">
-        <v>0.98</v>
+          <t>loanAccount.applicationFileId</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'purpose' → 'LOANPURPOSE1' (frequency=43)</t>
+          <t>Alias match (tier3): 'profileId' → 'APPLICATIONFILEID' (frequency=7)</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5199,7 +5190,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>residenceTypeCurrentAddress</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5214,25 +5205,25 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM17</t>
+          <t>LOANPURPOSE1</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
+          <t>loanAccount.loanPurpose1</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This describes the applicant's personal living situation (e.g., owned, rented) at their current address.</t>
+          <t>Alias match (tier1): 'purpose' → 'LOANPURPOSE1' (frequency=44)</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5244,7 +5235,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>residenceTypePermanentAddress</t>
+          <t>residenceTypeCurrentAddress</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5259,12 +5250,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM18</t>
+          <t>LOANAPPLICANTPARAM17</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
@@ -5277,7 +5268,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This describes the applicant's personal living situation (e.g., owned, rented) at their permanent address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This describes the applicant's personal living situation (e.g., owned, rented).</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5289,7 +5280,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>sanctionLetterLink</t>
+          <t>residenceTypePermanentAddress</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5299,30 +5290,30 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID28</t>
+          <t>LOANAPPLICANTPARAM18</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.27.documentId</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'sanctionLetterLink' → 'DOCUMENTID4' (frequency=6)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This describes the applicant's personal living situation (e.g., owned, rented).</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5334,7 +5325,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>sanctionLetterName</t>
+          <t>sanctionLetterLink</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5344,30 +5335,30 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME29</t>
+          <t>DOCUMENTID14</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.28.document</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="n">
-        <v>0.92</v>
+          <t>loanAccount.loanDocuments.13.documentId</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'sanctionLetterName' → 'DOCUMENTNAME2' (frequency=13)</t>
+          <t>Alias match (tier3): 'sanctionLetterLink' → 'DOCUMENTID4' (frequency=6)</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5379,7 +5370,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>stampDutyFeeAmountWithGst</t>
+          <t>sanctionLetterName</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5389,30 +5380,30 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>FEE4</t>
+          <t>DOCUMENTNAME15</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee4</t>
+          <t>loanAccount.loanDocuments.14.document</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (fee)</t>
+          <t>Alias match (tier2): 'sanctionLetterName' → 'DOCUMENTNAME2' (frequency=13)</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5424,7 +5415,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>tenure</t>
+          <t>stampDutyFeeAmountWithGst</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5434,30 +5425,30 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>tenure</t>
+          <t>FEE4</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.tenure</t>
+          <t>loanAccount.fee4</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'tenure' matches 'tenure'</t>
+          <t>Fee detection: field contains fee/charge keywords (fee)</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5469,7 +5460,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>tenureFrequency</t>
+          <t>tenure</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5484,25 +5475,25 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>REPAYMENTFREQUENCY</t>
+          <t>tenure</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.frequency</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.tenure</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'tenureFrequency' → 'REPAYMENTFREQUENCY' (frequency=6)</t>
+          <t>Exact match: normalized 'tenure' matches 'tenure'</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5514,7 +5505,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>totalExistingObligations</t>
+          <t>tenureFrequency</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5524,30 +5515,30 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER8</t>
+          <t>REPAYMENTFREQUENCY</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.8.value</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="n">
-        <v>0.9</v>
+          <t>loanAccount.frequency</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a summary financial metric of an applicant's existing debt, used as a key input for underwriting and eligibility calculation for the current loan.</t>
+          <t>Alias match (tier3): 'tenureFrequency' → 'REPAYMENTFREQUENCY' (frequency=7)</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -5559,7 +5550,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>totalNumberOfLoans</t>
+          <t>totalExistingObligations</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5569,21 +5560,21 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER9</t>
+          <t>LOANPARAMETER8</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.9.value</t>
+          <t>loanAccount.loanParameters.8.value</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -5592,7 +5583,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a bureau summary metric indicating the applicant's total active loans, used for underwriting the current application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a key financial input from bureau summary data used directly for underwriting calculation for the loan.</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -5604,7 +5595,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>totalNumberOfUnsecuredLoans</t>
+          <t>totalNumberOfLoans</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5619,16 +5610,16 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER10</t>
+          <t>LOANPARAMETER9</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.10.value</t>
+          <t>loanAccount.loanParameters.9.value</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -5637,7 +5628,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a bureau summary metric indicating the applicant's total unsecured loans, used for underwriting the current application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a bureau summary metric used as a key underwriting parameter to assess credit risk for the current loan application.</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5649,7 +5640,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>totalProcessingFeeAmountWithGst</t>
+          <t>totalNumberOfUnsecuredLoans</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5664,16 +5655,16 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER11</t>
+          <t>LOANPARAMETER10</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.11.value</t>
+          <t>loanAccount.loanParameters.10.value</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -5682,7 +5673,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific fee amount associated with the loan, a core part of the loan's cost structure.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a bureau summary metric used as a key underwriting parameter to assess credit risk for the current loan application.</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -5694,7 +5685,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>umrn</t>
+          <t>totalProcessingFeeAmountWithGst</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5704,17 +5695,17 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER12</t>
+          <t>LOANPARAMETER11</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.12.value</t>
+          <t>loanAccount.loanParameters.11.value</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
@@ -5727,7 +5718,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. UMRN (Unique Mandate Reference Number) is a unique identifier for the repayment mandate set up specifically for this loan.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific fee amount calculated for the loan application.</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -5739,7 +5730,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>valueOfTotalOutstandingLoans</t>
+          <t>umrn</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5749,17 +5740,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER13</t>
+          <t>LOANPARAMETER12</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.13.value</t>
+          <t>loanAccount.loanParameters.12.value</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
@@ -5772,7 +5763,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a key bureau summary financial metric of total loan exposure, used for underwriting the current loan application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is the Unique Mandate Reference Number for the loan's repayment mandate.</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -5784,7 +5775,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>30dpdInLast6Months</t>
+          <t>valueOfTotalOutstandingLoans</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5799,12 +5790,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER14</t>
+          <t>LOANPARAMETER13</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.14.value</t>
+          <t>loanAccount.loanParameters.13.value</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
@@ -5817,7 +5808,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific credit history attribute from a bureau report used as a direct input for the loan's underwriting and risk assessment.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a key financial metric from the credit bureau report used for underwriting the current loan application.</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -5829,7 +5820,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ckycImage</t>
+          <t>30dpdInLast6Months</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5844,25 +5835,25 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTKYC1IMAGE</t>
+          <t>LOANPARAMETER14</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.additionalKYCs.0.kyc1ImagePath</t>
+          <t>loanAccount.loanParameters.14.value</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'ckycImage' → 'APPLICANTKYC1IMAGE' (frequency=5)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific credit bureau summary metric used as a key input for underwriting and risk assessment of the loan application.</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -5874,7 +5865,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ckycNumber</t>
+          <t>ckycImage</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5889,12 +5880,12 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTKYC1NUMBER</t>
+          <t>APPLICANTKYC1IMAGE</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.additionalKYCs.0.kyc1ProofNumber</t>
+          <t>loanAccount.customer.additionalKYCs.0.kyc1ImagePath</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
@@ -5907,7 +5898,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'ckycNumber' → 'APPLICANTKYC1NUMBER' (frequency=6)</t>
+          <t>Alias match (tier3): 'ckycImage' → 'APPLICANTKYC1IMAGE' (frequency=5)</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -5919,7 +5910,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ckycType</t>
+          <t>ckycNumber</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5934,12 +5925,12 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTKYC1TYPE</t>
+          <t>APPLICANTKYC1NUMBER</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.additionalKYCs.0.kyc1ProofType</t>
+          <t>loanAccount.customer.additionalKYCs.0.kyc1ProofNumber</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
@@ -5952,7 +5943,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'ckycType' → 'APPLICANTKYC1TYPE' (frequency=5)</t>
+          <t>Alias match (tier3): 'ckycNumber' → 'APPLICANTKYC1NUMBER' (frequency=6)</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -5964,7 +5955,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>clearingCharges</t>
+          <t>ckycType</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5974,30 +5965,30 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER15</t>
+          <t>APPLICANTKYC1TYPE</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.15.value</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.additionalKYCs.0.kyc1ProofType</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This represents a specific fee or charge associated with the loan's repayment process.</t>
+          <t>Alias match (tier3): 'ckycType' → 'APPLICANTKYC1TYPE' (frequency=5)</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6009,7 +6000,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>continuityOfJob</t>
+          <t>clearingCharges</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6019,17 +6010,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM19</t>
+          <t>LOANPARAMETER15</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.18.value</t>
+          <t>loanAccount.loanParameters.15.value</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
@@ -6042,7 +6033,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This describes the stability and duration of the applicant's employment, which is a personal profile attribute.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a type of fee or charge associated with the loan.</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6054,7 +6045,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>documentCharges</t>
+          <t>continuityOfJob</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6064,30 +6055,30 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>FEE5</t>
+          <t>LOANAPPLICANTPARAM19</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee5</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.18.value</t>
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (charges, charge)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This describes the applicant's employment history and stability.</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -6099,7 +6090,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>dpdInLast12Months</t>
+          <t>documentCharges</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6109,17 +6100,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER16</t>
+          <t>FEE5</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.16.value</t>
+          <t>loanAccount.fee5</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
@@ -6127,12 +6118,12 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a credit history metric from a bureau report, indicating delinquency, used as a direct input for the loan's underwriting decision.</t>
+          <t>Fee detection: field contains fee/charge keywords (charge, charges)</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -6144,7 +6135,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>nameOfBureau</t>
+          <t>dpdInLast12Months</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6159,25 +6150,25 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>NAMEOFBUREAU</t>
+          <t>LOANPARAMETER16</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>customer.cbRemarks</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.loanParameters.16.value</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'nameOfBureau' matches 'NAMEOFBUREAU'</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific credit bureau summary metric used as a key input for underwriting and risk assessment of the loan application.</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -6189,7 +6180,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>officeCity</t>
+          <t>nameOfBureau</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6204,12 +6195,12 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM20</t>
+          <t>NAMEOFBUREAU</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.19.value</t>
+          <t>customer.cbRemarks</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
@@ -6217,12 +6208,12 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's employment address information.</t>
+          <t>Exact match: normalized 'nameOfBureau' matches 'NAMEOFBUREAU'</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -6234,7 +6225,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>officePincode</t>
+          <t>officeCity</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6249,12 +6240,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM21</t>
+          <t>LOANAPPLICANTPARAM20</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.20.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.19.value</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
@@ -6267,7 +6258,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's employment address information.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field describes the applicant's office address, which is part of their employment profile.</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -6279,7 +6270,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>officeState</t>
+          <t>officePincode</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6294,12 +6285,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM22</t>
+          <t>LOANAPPLICANTPARAM21</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.21.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.20.value</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
@@ -6312,7 +6303,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is part of the applicant's employment address information.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field describes the applicant's office address, which is part of their employment profile.</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -6324,7 +6315,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>okycImage</t>
+          <t>officeState</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6339,25 +6330,25 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTKYC3IMAGE</t>
+          <t>LOANAPPLICANTPARAM22</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.additionalKYCs.2.kyc1ImagePath</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.21.value</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'okycImage' → 'APPLICANTKYC3IMAGE' (frequency=4)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field describes the applicant's office address, which is part of their employment profile.</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -6369,7 +6360,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>okycNumber</t>
+          <t>okycImage</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6384,25 +6375,25 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM23</t>
+          <t>APPLICANTKYC3IMAGE</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.22.value</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.additionalKYCs.2.kyc1ImagePath</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a number related to the applicant's Offline KYC documentation and identity verification.</t>
+          <t>Alias match (tier3): 'okycImage' → 'APPLICANTKYC3IMAGE' (frequency=4)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -6414,7 +6405,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>okycType</t>
+          <t>okycNumber</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6429,25 +6420,25 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTKYC3TYPE</t>
+          <t>LOANAPPLICANTPARAM23</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.additionalKYCs.2.kyc1ProofType</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.22.value</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'okycType' → 'APPLICANTKYC3TYPE' (frequency=4)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is an identifier related to the applicant's KYC verification process.</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -6459,7 +6450,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>overallOutstanding</t>
+          <t>okycType</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6469,30 +6460,30 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER17</t>
+          <t>APPLICANTKYC3TYPE</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.17.value</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.additionalKYCs.2.kyc1ProofType</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a bureau summary financial metric of total outstanding debt, used as a key input for underwriting and eligibility calculation.</t>
+          <t>Alias match (tier3): 'okycType' → 'APPLICANTKYC3TYPE' (frequency=4)</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -6504,7 +6495,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>siteVisitCharge</t>
+          <t>overallOutstanding</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6514,21 +6505,21 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER18</t>
+          <t>LOANPARAMETER17</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.18.value</t>
+          <t>loanAccount.loanParameters.17.value</t>
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -6537,7 +6528,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific fee charged as part of the loan application and verification process.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a key bureau summary metric representing the applicant's total debt, used for underwriting the loan.</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -6549,7 +6540,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>totalInsurancePremiumAmountWithGst</t>
+          <t>siteVisitCharge</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6559,30 +6550,30 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTINSURANCEAMT</t>
+          <t>LOANPARAMETER18</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.portfolioInsurancePremium</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.18.value</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'totalInsurancePremiumAmountWithGst' → 'APPLICANTINSURANCEAMT' (frequency=5)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific fee or charge associated with the loan application process.</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -6594,7 +6585,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>vkycImage</t>
+          <t>totalInsurancePremiumAmountWithGst</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6609,12 +6600,12 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTKYC2IMAGE</t>
+          <t>APPLICANTINSURANCEAMT</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.additionalKYCs.1.kyc1ImagePath</t>
+          <t>loanAccount.portfolioInsurancePremium</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
@@ -6627,7 +6618,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'vkycImage' → 'APPLICANTKYC2IMAGE' (frequency=4)</t>
+          <t>Alias match (tier3): 'totalInsurancePremiumAmountWithGst' → 'APPLICANTINSURANCEAMT' (frequency=5)</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -6639,7 +6630,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>vkycNumber</t>
+          <t>vkycImage</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6654,25 +6645,25 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM24</t>
+          <t>APPLICANTKYC2IMAGE</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.23.value</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.additionalKYCs.1.kyc1ImagePath</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a reference number for the applicant's Video KYC process, which is part of their identity verification.</t>
+          <t>Alias match (tier3): 'vkycImage' → 'APPLICANTKYC2IMAGE' (frequency=4)</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -6684,7 +6675,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>vkycType</t>
+          <t>vkycNumber</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6699,25 +6690,25 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTKYC2TYPE</t>
+          <t>LOANAPPLICANTPARAM24</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.additionalKYCs.1.kyc1ProofType</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.23.value</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'vkycType' → 'APPLICANTKYC2TYPE' (frequency=4)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is an identifier related to the applicant's KYC verification process.</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -6729,7 +6720,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>vkycVideo</t>
+          <t>vkycType</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6739,17 +6730,17 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID30</t>
+          <t>APPLICANTKYC2TYPE</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.29.documentId</t>
+          <t>loanAccount.customer.additionalKYCs.1.kyc1ProofType</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
@@ -6762,7 +6753,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'vkycVideo' → 'DOCUMENTID15' (frequency=4)</t>
+          <t>Alias match (tier3): 'vkycType' → 'APPLICANTKYC2TYPE' (frequency=4)</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -6774,7 +6765,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>writeOffHistory</t>
+          <t>vkycVideo</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6784,30 +6775,30 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER19</t>
+          <t>DOCUMENTID15</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.19.value</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="n">
-        <v>1</v>
+          <t>loanAccount.loanDocuments.14.documentId</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>0.85</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a critical credit history flag from a bureau report used to make an underwriting decision on the loan application.</t>
+          <t>Alias match (tier3): 'vkycVideo' → 'DOCUMENTID15' (frequency=4)</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -6819,7 +6810,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>loanType</t>
+          <t>writeOffHistory</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6829,30 +6820,30 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTLOANTYPE</t>
+          <t>LOANPARAMETER19</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanType</t>
+          <t>loanAccount.loanParameters.19.value</t>
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>0.9412</v>
+        <v>0.9</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy: 'loanType' ~ 'APPLICANTLOANTYPE' score=0.94</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a critical credit history flag from the bureau report used for underwriting and risk assessment of the loan.</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -6862,47 +6853,47 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>insuranceAmountWithGst</t>
         </is>
       </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM25</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
-        </is>
-      </c>
-      <c r="F142" s="6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>llm_loanapplicantparam</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="inlineStr">
-        <is>
-          <t>The field represents a specific loan-related financial parameter for the applicant and does not match any specific excel_key.</t>
-        </is>
-      </c>
-      <c r="I142" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>FEE6</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.fee6</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>llm_pattern_fee</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>The field 'insuranceAmountWithGst' represents a charge related to insurance which is a type of fee.</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -6919,30 +6910,30 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>LOANPARAMETER20</t>
+          <t>LOANAPPLICANTPARAM25</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.20.value</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="n">
-        <v>0.1</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>0.72</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. The field name 'as' is a stop word and lacks discernible business meaning. As it is not clearly a customer-person detail, it is placed in the default LOANPARAMETER bucket with very low confidence.</t>
+          <t>The field 'as' is ambiguous and cannot be matched to a specific key, so it is mapped as a loan applicant parameter.</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
@@ -6964,17 +6955,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME31</t>
+          <t>DOCUMENTNAME16</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.30.document</t>
+          <t>loanAccount.loanDocuments.15.document</t>
         </is>
       </c>
       <c r="F144" s="4" t="n">
@@ -6987,7 +6978,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>The field 'loanAggreementName' contains the document keyword 'agreement' and the suffix 'Name' indicating it is the name of a document.</t>
+          <t>The field name contains the document keyword 'loan agreement' and 'name' suggesting it is a document name.</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -7008,7 +6999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7049,7 +7040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-07 11:01:15</t>
+          <t>2026-04-07 14:53:22</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7050,7 @@
           <t>Total Fields Mapped:</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>143</v>
       </c>
     </row>
@@ -7084,7 +7075,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Breakdown by Match Type:</t>
         </is>
@@ -7107,7 +7098,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -7117,57 +7108,57 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>alias_tier4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>document_name</t>
+          <t>document_id</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>document_name</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -7187,7 +7178,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -7200,149 +7191,159 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>llm_pattern_fee</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Breakdown by Entity:</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
+          <t>FEE</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
           <t>LOAN</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Fields Needing Review:</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B29" s="9" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
+    <row r="30">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Fields:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>insuranceAmountWithGst</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
+          <t>loanType</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
           <t>as</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Mandatory Fields Missing:</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B35" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Confidence Distribution:</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>0.90-1.00</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>88</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>0.80-0.89</t>
+          <t>0.90-1.00</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.70-0.79</t>
+          <t>0.80-0.89</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
+          <t>0.70-0.79</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
           <t>0.00-0.69</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
+      <c r="C42" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7420,7 +7421,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>insuranceAmountWithGst</t>
+          <t>loanType</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -7430,30 +7431,30 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM25</t>
+          <t>APPLICANTCUSTOMERTYPE</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
+          <t>loanAccount.customer.customerType</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>llm_loanapplicantparam</t>
+          <t>alias_tier4</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>The field represents a specific loan-related financial parameter for the applicant and does not match any specific excel_key.</t>
+          <t>Alias match (tier4): 'loanType' → 'APPLICANTCUSTOMERTYPE' (frequency=1)</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -7475,30 +7476,30 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>LOANPARAMETER20</t>
+          <t>LOANAPPLICANTPARAM25</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.20.value</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>0.1</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>0.72</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. The field name 'as' is a stop word and lacks discernible business meaning. As it is not clearly a customer-person detail, it is placed in the default LOANPARAMETER bucket with very low confidence.</t>
+          <t>The field 'as' is ambiguous and cannot be matched to a specific key, so it is mapped as a loan applicant parameter.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
